--- a/artfynd/A 31162-2025 artfynd.xlsx
+++ b/artfynd/A 31162-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>103057403</v>
+        <v>103284665</v>
       </c>
       <c r="B2" t="n">
-        <v>90647</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93222</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,26 +686,26 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4362</v>
+        <v>3100</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Phellodon fuligineoalbus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(J.C.Schmidt) Baird</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -725,10 +720,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>719192.8409204908</v>
+        <v>719040</v>
       </c>
       <c r="R2" t="n">
-        <v>7216566.638019831</v>
+        <v>7216479</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -755,22 +750,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2022-08-23</t>
+          <t>2022-08-31</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2022-08-23</t>
+          <t>2022-08-31</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -794,6 +789,235 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>103057403</v>
+      </c>
+      <c r="B3" t="n">
+        <v>93191</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>4362</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Blå taggsvamp</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Hydnellum caeruleum</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Hornem.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Norsjö, Vb</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>719193</v>
+      </c>
+      <c r="R3" t="n">
+        <v>7216567</v>
+      </c>
+      <c r="S3" t="n">
+        <v>25</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2022-08-23</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>08:11</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2022-08-23</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>08:11</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Helena Gustafsson</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Helena Gustafsson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>103284649</v>
+      </c>
+      <c r="B4" t="n">
+        <v>93191</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>4362</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Blå taggsvamp</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Hydnellum caeruleum</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Hornem.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Norsjö, Vb</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>719058</v>
+      </c>
+      <c r="R4" t="n">
+        <v>7216494</v>
+      </c>
+      <c r="S4" t="n">
+        <v>25</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2022-08-31</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>14:29</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2022-08-31</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>14:29</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Helena Gustafsson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Helena Gustafsson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
